--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.21672857196631</v>
+        <v>5.885218392944526</v>
       </c>
       <c r="D2" t="n">
-        <v>59.15230179420452</v>
+        <v>9.612249041558234</v>
       </c>
       <c r="E2" t="n">
-        <v>9.572356909898954</v>
+        <v>1.55550799785858</v>
       </c>
       <c r="F2" t="n">
-        <v>12.68700592687761</v>
+        <v>2.061638463117611</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.84582637988407</v>
+        <v>5.337446786731161</v>
       </c>
       <c r="D3" t="n">
-        <v>33.04782349186416</v>
+        <v>5.370271317427927</v>
       </c>
       <c r="E3" t="n">
-        <v>9.572356909898954</v>
+        <v>1.55550799785858</v>
       </c>
       <c r="F3" t="n">
-        <v>12.68700592687761</v>
+        <v>2.061638463117611</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.99228547685494</v>
+        <v>5.361246389988928</v>
       </c>
       <c r="D4" t="n">
-        <v>32.99751348690052</v>
+        <v>5.362095941621336</v>
       </c>
       <c r="E4" t="n">
-        <v>9.572356909898954</v>
+        <v>1.55550799785858</v>
       </c>
       <c r="F4" t="n">
-        <v>12.68700592687761</v>
+        <v>2.061638463117611</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.82598801165984</v>
+        <v>3.871723051894724</v>
       </c>
       <c r="D5" t="n">
-        <v>40.72976943564247</v>
+        <v>6.618587533291902</v>
       </c>
       <c r="E5" t="n">
-        <v>9.572356909898954</v>
+        <v>1.55550799785858</v>
       </c>
       <c r="F5" t="n">
-        <v>12.68700592687761</v>
+        <v>2.061638463117611</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.29262708095829</v>
+        <v>4.922551900655723</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67672124091299</v>
+        <v>4.98496720164836</v>
       </c>
       <c r="E6" t="n">
-        <v>9.572356909898954</v>
+        <v>1.55550799785858</v>
       </c>
       <c r="F6" t="n">
-        <v>12.68700592687761</v>
+        <v>2.061638463117611</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.39061768636521</v>
+        <v>6.725975374034347</v>
       </c>
       <c r="D7" t="n">
-        <v>40.97781885148381</v>
+        <v>6.658895563366119</v>
       </c>
       <c r="E7" t="n">
-        <v>9.572356909898954</v>
+        <v>1.55550799785858</v>
       </c>
       <c r="F7" t="n">
-        <v>12.68700592687761</v>
+        <v>2.061638463117611</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.54518226051788</v>
+        <v>7.401092117334155</v>
       </c>
       <c r="D8" t="n">
-        <v>50.59590916425863</v>
+        <v>8.221835239192027</v>
       </c>
       <c r="E8" t="n">
-        <v>9.572356909898954</v>
+        <v>1.55550799785858</v>
       </c>
       <c r="F8" t="n">
-        <v>12.68700592687761</v>
+        <v>2.061638463117611</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.0843535395937</v>
+        <v>1.963707450183976</v>
       </c>
       <c r="D9" t="n">
-        <v>13.97640356275242</v>
+        <v>2.271165578947269</v>
       </c>
       <c r="E9" t="n">
-        <v>9.572356909898954</v>
+        <v>1.55550799785858</v>
       </c>
       <c r="F9" t="n">
-        <v>12.68700592687761</v>
+        <v>2.061638463117611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.2009889729451</v>
+        <v>3.770160708103579</v>
       </c>
       <c r="D10" t="n">
-        <v>24.93754964386322</v>
+        <v>4.052351817127773</v>
       </c>
       <c r="E10" t="n">
-        <v>9.572356909898954</v>
+        <v>1.55550799785858</v>
       </c>
       <c r="F10" t="n">
-        <v>12.68700592687761</v>
+        <v>2.061638463117611</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
